--- a/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/ground truths/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588CED15-E8FF-7C42-A686-81AD3BBD71C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15901732-B1E8-B048-9B80-D0025964E552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="740" windowWidth="27900" windowHeight="16460" activeTab="1" xr2:uid="{CB0C4F64-FD59-E444-AAE5-C8229608F4B9}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{CB0C4F64-FD59-E444-AAE5-C8229608F4B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="1" r:id="rId1"/>
@@ -71,9 +71,6 @@
     <t>CF_M08_AU03</t>
   </si>
   <si>
-    <t>Traffic</t>
-  </si>
-  <si>
     <t>Security Service (Traefik)</t>
   </si>
   <si>
@@ -414,6 +411,9 @@
   </si>
   <si>
     <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
+  </si>
+  <si>
+    <t>Traefik</t>
   </si>
 </sst>
 </file>
@@ -929,25 +929,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="C1" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="D1" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="E1" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="F1" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="G1" s="24" t="s">
         <v>104</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -1007,13 +1007,13 @@
         <v>2</v>
       </c>
       <c r="D4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>13</v>
       </c>
       <c r="G4" s="12">
         <v>41</v>
@@ -1024,16 +1024,16 @@
         <v>0</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>5</v>
@@ -1047,17 +1047,17 @@
         <v>0</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>18</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>19</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>20</v>
       </c>
       <c r="G6" s="16">
         <v>42</v>
@@ -1068,19 +1068,19 @@
         <v>0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="G7" s="8">
         <v>42</v>
@@ -1091,19 +1091,19 @@
         <v>0</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="F8" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" s="12">
         <v>42</v>
@@ -1114,17 +1114,17 @@
         <v>0</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>30</v>
       </c>
       <c r="G9" s="20">
         <v>42</v>
@@ -1135,17 +1135,17 @@
         <v>0</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="G10" s="16">
         <v>42</v>
@@ -1156,17 +1156,17 @@
         <v>0</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="18" t="s">
         <v>35</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>36</v>
       </c>
       <c r="G11" s="20">
         <v>42</v>
@@ -1177,17 +1177,17 @@
         <v>0</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>38</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>39</v>
       </c>
       <c r="G12" s="16">
         <v>42</v>
@@ -1198,17 +1198,17 @@
         <v>0</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>42</v>
       </c>
       <c r="G13" s="20">
         <v>42</v>
@@ -1219,17 +1219,17 @@
         <v>0</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>44</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>45</v>
       </c>
       <c r="G14" s="16">
         <v>42</v>
@@ -1240,16 +1240,16 @@
         <v>0</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>5</v>
@@ -1263,19 +1263,19 @@
         <v>0</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="F16" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="G16" s="12">
         <v>42</v>
@@ -1286,19 +1286,19 @@
         <v>0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="G17" s="8">
         <v>42</v>
@@ -1309,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>5</v>
@@ -1332,19 +1332,19 @@
         <v>0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="F19" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="G19" s="8">
         <v>42</v>
@@ -1355,16 +1355,16 @@
         <v>0</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>5</v>
@@ -1378,19 +1378,19 @@
         <v>0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="F21" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="G21" s="8">
         <v>42</v>
@@ -1401,16 +1401,16 @@
         <v>0</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>5</v>
@@ -1424,19 +1424,19 @@
         <v>0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="F23" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="G23" s="8">
         <v>42</v>
@@ -1447,16 +1447,16 @@
         <v>0</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>5</v>
@@ -1470,19 +1470,19 @@
         <v>0</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="F25" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="G25" s="8">
         <v>42</v>
@@ -1493,16 +1493,16 @@
         <v>0</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>5</v>
@@ -1516,19 +1516,19 @@
         <v>0</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="F27" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="G27" s="8">
         <v>42</v>
@@ -1539,16 +1539,16 @@
         <v>0</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>5</v>
@@ -1562,19 +1562,19 @@
         <v>0</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D29" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="G29" s="8">
         <v>42</v>
@@ -1585,16 +1585,16 @@
         <v>0</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D30" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>5</v>
@@ -1608,16 +1608,16 @@
         <v>0</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C31" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D31" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="32" t="s">
         <v>97</v>
-      </c>
-      <c r="E31" s="32" t="s">
-        <v>98</v>
       </c>
       <c r="F31" s="33"/>
       <c r="G31" s="23">
@@ -1644,25 +1644,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C1" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="E1" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="F1" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="G1" s="24" t="s">
         <v>104</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="56" x14ac:dyDescent="0.2">
@@ -1673,13 +1673,13 @@
         <v>5</v>
       </c>
       <c r="C2" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="E2" s="27" t="s">
         <v>108</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>109</v>
       </c>
       <c r="F2" s="26"/>
       <c r="G2" s="26">
@@ -1691,19 +1691,19 @@
         <v>0</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="E3" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="F3" s="25" t="s">
         <v>112</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>113</v>
       </c>
       <c r="G3" s="28">
         <v>42</v>
@@ -1714,16 +1714,16 @@
         <v>0</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="27" t="s">
+      <c r="E4" s="27" t="s">
         <v>115</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>116</v>
       </c>
       <c r="F4" s="26"/>
       <c r="G4" s="26">
@@ -1735,16 +1735,16 @@
         <v>0</v>
       </c>
       <c r="B5" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="30" t="s">
+      <c r="E5" s="29" t="s">
         <v>118</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>119</v>
       </c>
       <c r="F5" s="28"/>
       <c r="G5" s="28">
@@ -1756,16 +1756,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="31" t="s">
+      <c r="E6" s="27" t="s">
         <v>121</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>122</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="26">
@@ -1777,16 +1777,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" s="30" t="s">
+      <c r="E7" s="29" t="s">
         <v>124</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>125</v>
       </c>
       <c r="F7" s="28"/>
       <c r="G7" s="28">

--- a/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15901732-B1E8-B048-9B80-D0025964E552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CECBE0A-5AF6-064B-9174-BFF978FF92DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{CB0C4F64-FD59-E444-AAE5-C8229608F4B9}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17000" xr2:uid="{CB0C4F64-FD59-E444-AAE5-C8229608F4B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>These services run on Amazon EC2 instances</t>
   </si>
   <si>
-    <t>CF_M08_AD01</t>
-  </si>
-  <si>
     <t>CF_M08_AU02</t>
   </si>
   <si>
@@ -203,9 +200,6 @@
     <t>Prisma as ORM</t>
   </si>
   <si>
-    <t>CF_M08_AD02</t>
-  </si>
-  <si>
     <t>CF_M08_AU10</t>
   </si>
   <si>
@@ -263,9 +257,6 @@
     <t>CF_M08_AU16</t>
   </si>
   <si>
-    <t>Analysis</t>
-  </si>
-  <si>
     <t>CF_M08_AU17</t>
   </si>
   <si>
@@ -305,9 +296,6 @@
     <t>CF_M08_AU21</t>
   </si>
   <si>
-    <t>Briefly</t>
-  </si>
-  <si>
     <t>Connects to Brevo to create, send and schedule emails.</t>
   </si>
   <si>
@@ -353,9 +341,6 @@
     <t>Page Number</t>
   </si>
   <si>
-    <t>AD ID</t>
-  </si>
-  <si>
     <t>Architectural Pattern</t>
   </si>
   <si>
@@ -377,36 +362,24 @@
     <t>CF_M09_AU04</t>
   </si>
   <si>
-    <t>CF_M08_AD03</t>
-  </si>
-  <si>
     <t>Component-based</t>
   </si>
   <si>
     <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components</t>
   </si>
   <si>
-    <t>CF_M08_AD04</t>
-  </si>
-  <si>
     <t>Observer</t>
   </si>
   <si>
     <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
   </si>
   <si>
-    <t>CF_M08_AD05</t>
-  </si>
-  <si>
     <t>Singleton</t>
   </si>
   <si>
     <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, records or connections to databases, where having multiple instances could lead to inconsistent states or inefficient use of resources</t>
   </si>
   <si>
-    <t>CF_M08_AD06</t>
-  </si>
-  <si>
     <t>Client-Server</t>
   </si>
   <si>
@@ -414,6 +387,33 @@
   </si>
   <si>
     <t>Traefik</t>
+  </si>
+  <si>
+    <t>CF_M08_P01</t>
+  </si>
+  <si>
+    <t>CF_M08_P02</t>
+  </si>
+  <si>
+    <t>P ID</t>
+  </si>
+  <si>
+    <t>CF_M08_P03</t>
+  </si>
+  <si>
+    <t>CF_M08_P04</t>
+  </si>
+  <si>
+    <t>CF_M08_P05</t>
+  </si>
+  <si>
+    <t>CF_M08_P06</t>
+  </si>
+  <si>
+    <t>Brevo</t>
+  </si>
+  <si>
+    <t>Analytics</t>
   </si>
 </sst>
 </file>
@@ -929,25 +929,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="F1" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="G1" s="24" t="s">
         <v>100</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -967,7 +967,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G2" s="4">
         <v>41</v>
@@ -978,19 +978,19 @@
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="F3" s="6" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G3" s="8">
         <v>41</v>
@@ -1001,19 +1001,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>11</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>12</v>
       </c>
       <c r="G4" s="12">
         <v>41</v>
@@ -1024,19 +1024,19 @@
         <v>0</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" s="6" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G5" s="8">
         <v>42</v>
@@ -1047,17 +1047,17 @@
         <v>0</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>18</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>19</v>
       </c>
       <c r="G6" s="16">
         <v>42</v>
@@ -1068,19 +1068,19 @@
         <v>0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="G7" s="8">
         <v>42</v>
@@ -1091,19 +1091,19 @@
         <v>0</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="12">
         <v>42</v>
@@ -1114,17 +1114,17 @@
         <v>0</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>28</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>29</v>
       </c>
       <c r="G9" s="20">
         <v>42</v>
@@ -1135,17 +1135,17 @@
         <v>0</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>31</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>32</v>
       </c>
       <c r="G10" s="16">
         <v>42</v>
@@ -1156,17 +1156,17 @@
         <v>0</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="18" t="s">
         <v>34</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>35</v>
       </c>
       <c r="G11" s="20">
         <v>42</v>
@@ -1177,17 +1177,17 @@
         <v>0</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>37</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>38</v>
       </c>
       <c r="G12" s="16">
         <v>42</v>
@@ -1198,17 +1198,17 @@
         <v>0</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>41</v>
       </c>
       <c r="G13" s="20">
         <v>42</v>
@@ -1219,17 +1219,17 @@
         <v>0</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>44</v>
       </c>
       <c r="G14" s="16">
         <v>42</v>
@@ -1240,19 +1240,19 @@
         <v>0</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="E15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="F15" s="6" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G15" s="8">
         <v>42</v>
@@ -1263,19 +1263,19 @@
         <v>0</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="F16" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="G16" s="12">
         <v>42</v>
@@ -1286,19 +1286,19 @@
         <v>0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="F17" s="6" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="G17" s="8">
         <v>42</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G18" s="12">
         <v>42</v>
@@ -1332,19 +1332,19 @@
         <v>0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="G19" s="8">
         <v>42</v>
@@ -1355,19 +1355,19 @@
         <v>0</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G20" s="12">
         <v>42</v>
@@ -1378,19 +1378,19 @@
         <v>0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="G21" s="8">
         <v>42</v>
@@ -1401,19 +1401,19 @@
         <v>0</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G22" s="12">
         <v>42</v>
@@ -1424,19 +1424,19 @@
         <v>0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="G23" s="8">
         <v>42</v>
@@ -1447,19 +1447,19 @@
         <v>0</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G24" s="12">
         <v>42</v>
@@ -1470,19 +1470,19 @@
         <v>0</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G25" s="8">
         <v>42</v>
@@ -1493,19 +1493,19 @@
         <v>0</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G26" s="12">
         <v>42</v>
@@ -1516,19 +1516,19 @@
         <v>0</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G27" s="8">
         <v>42</v>
@@ -1539,19 +1539,19 @@
         <v>0</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G28" s="12">
         <v>42</v>
@@ -1562,19 +1562,19 @@
         <v>0</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G29" s="8">
         <v>42</v>
@@ -1585,19 +1585,19 @@
         <v>0</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G30" s="12">
         <v>42</v>
@@ -1608,16 +1608,16 @@
         <v>0</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C31" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F31" s="33"/>
       <c r="G31" s="23">
@@ -1644,25 +1644,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C1" s="24" t="s">
+      <c r="F1" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="24" t="s">
         <v>100</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="56" x14ac:dyDescent="0.2">
@@ -1670,16 +1670,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F2" s="26"/>
       <c r="G2" s="26">
@@ -1691,19 +1691,19 @@
         <v>0</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G3" s="28">
         <v>42</v>
@@ -1714,16 +1714,16 @@
         <v>0</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C4" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="27" t="s">
         <v>109</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>115</v>
       </c>
       <c r="F4" s="26"/>
       <c r="G4" s="26">
@@ -1735,37 +1735,37 @@
         <v>0</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F5" s="28"/>
       <c r="G5" s="28">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="26">
@@ -1777,16 +1777,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F7" s="28"/>
       <c r="G7" s="28">

--- a/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CECBE0A-5AF6-064B-9174-BFF978FF92DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FED029-EF7C-124A-B44C-3DEA7AB1033F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17000" xr2:uid="{CB0C4F64-FD59-E444-AAE5-C8229608F4B9}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" activeTab="1" xr2:uid="{CB0C4F64-FD59-E444-AAE5-C8229608F4B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="101">
   <si>
     <t>CF_M08</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Security Service (Traefik)</t>
   </si>
   <si>
-    <t>CF_M00_AU02</t>
-  </si>
-  <si>
     <t>CF_M08_AU04</t>
   </si>
   <si>
@@ -104,9 +101,6 @@
     <t>System Service (Next.js)</t>
   </si>
   <si>
-    <t>CF_M00_AU04</t>
-  </si>
-  <si>
     <t>CF_M08_AU06</t>
   </si>
   <si>
@@ -122,54 +116,6 @@
     <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
   </si>
   <si>
-    <t>CF_M08_AU04, CF_M08_AU10</t>
-  </si>
-  <si>
-    <t>CF_M08_AU26</t>
-  </si>
-  <si>
-    <t>• Interacts with various external services for specific functionalities […] Cloud storage</t>
-  </si>
-  <si>
-    <t>CF_M08_AU04, CF_M08_AU12</t>
-  </si>
-  <si>
-    <t>CF_M08_AU27</t>
-  </si>
-  <si>
-    <t>• Interacts with various external services for specific functionalities […] Payment processing</t>
-  </si>
-  <si>
-    <t>CF_M08_AU04, CF_M08_AU14</t>
-  </si>
-  <si>
-    <t>CF_M08_AU28</t>
-  </si>
-  <si>
-    <t>• Interacts with various external services for specific functionalities […] Analysis</t>
-  </si>
-  <si>
-    <t>CF_M08_AU04, CF_M08_AU16</t>
-  </si>
-  <si>
-    <t>CF_M08_AU29</t>
-  </si>
-  <si>
-    <t>• Interacts with various external services for specific functionalities [...] Error monitoring</t>
-  </si>
-  <si>
-    <t>CF_M08_AU04, CF_M08_AU18</t>
-  </si>
-  <si>
-    <t>CF_M08_AU30</t>
-  </si>
-  <si>
-    <t>• Interacts with various external services for specific functionalities [...] Correo electrónico</t>
-  </si>
-  <si>
-    <t>CF_M08_AU04, CF_M08_AU20</t>
-  </si>
-  <si>
     <t>CF_M08_AU07</t>
   </si>
   <si>
@@ -188,9 +134,6 @@
     <t>Data Service (PostgreSQL)</t>
   </si>
   <si>
-    <t>CF_M09_AU07</t>
-  </si>
-  <si>
     <t>CF_M08_AU09</t>
   </si>
   <si>
@@ -215,9 +158,6 @@
     <t>Use Google for user authentication</t>
   </si>
   <si>
-    <t>CF_M09_AU09</t>
-  </si>
-  <si>
     <t>CF_M08_AU12</t>
   </si>
   <si>
@@ -233,9 +173,6 @@
     <t>Amazon S3 (for cloud)</t>
   </si>
   <si>
-    <t>CF_M09_AU11</t>
-  </si>
-  <si>
     <t>CF_M08_AU14</t>
   </si>
   <si>
@@ -251,9 +188,6 @@
     <t>Integrate with Stripe to handle payments and subscriptions</t>
   </si>
   <si>
-    <t>CF_M09_AU13</t>
-  </si>
-  <si>
     <t>CF_M08_AU16</t>
   </si>
   <si>
@@ -266,9 +200,6 @@
     <t>Implement Google Analytics to track and analyze site traffic</t>
   </si>
   <si>
-    <t>CF_M09_AU15</t>
-  </si>
-  <si>
     <t>CF_M08_AU18</t>
   </si>
   <si>
@@ -284,9 +215,6 @@
     <t>Use Sentry to track and manage errors in the application</t>
   </si>
   <si>
-    <t>CF_M09_AU17</t>
-  </si>
-  <si>
     <t>CF_M08_AU20</t>
   </si>
   <si>
@@ -299,9 +227,6 @@
     <t>Connects to Brevo to create, send and schedule emails.</t>
   </si>
   <si>
-    <t>CF_M09_AU19</t>
-  </si>
-  <si>
     <t>CF_M08_AU22</t>
   </si>
   <si>
@@ -359,9 +284,6 @@
     <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
   </si>
   <si>
-    <t>CF_M09_AU04</t>
-  </si>
-  <si>
     <t>Component-based</t>
   </si>
   <si>
@@ -414,6 +336,9 @@
   </si>
   <si>
     <t>Analytics</t>
+  </si>
+  <si>
+    <t>CF_M08_AU04, CF_M08_AU10, CF_M08_AU12, CF_M08_AU14, CF_M08_AU16, CF_M08_AU18, CF_M08_AU20</t>
   </si>
 </sst>
 </file>
@@ -924,30 +849,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D99AB4DB-819F-1A4D-945A-3D2CEBF42CB0}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -967,7 +892,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="G2" s="4">
         <v>41</v>
@@ -990,7 +915,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="G3" s="8">
         <v>41</v>
@@ -1007,13 +932,13 @@
         <v>2</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G4" s="12">
         <v>41</v>
@@ -1024,19 +949,19 @@
         <v>0</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>14</v>
-      </c>
       <c r="F5" s="6" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="G5" s="8">
         <v>42</v>
@@ -1047,17 +972,17 @@
         <v>0</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>16</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>17</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>18</v>
       </c>
       <c r="G6" s="16">
         <v>42</v>
@@ -1068,19 +993,19 @@
         <v>0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>21</v>
-      </c>
       <c r="F7" s="6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G7" s="8">
         <v>42</v>
@@ -1091,19 +1016,19 @@
         <v>0</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G8" s="12">
         <v>42</v>
@@ -1114,522 +1039,417 @@
         <v>0</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="20">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="E10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="20">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="14" t="s">
+      <c r="F10" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15" t="s">
+      <c r="C11" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="E11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="16">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="18" t="s">
+      <c r="F11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19" t="s">
+      <c r="C12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="E12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="20">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="14" t="s">
+      <c r="F12" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15" t="s">
+      <c r="C13" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="E13" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="16">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="18" t="s">
+      <c r="C14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19" t="s">
+      <c r="E14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="20">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="14" t="s">
+      <c r="C15" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="14" t="s">
+      <c r="E15" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="16">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="E16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="F16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="D17" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G15" s="8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="10" t="s">
+      <c r="E17" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C18" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D18" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E18" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G16" s="12">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="6" t="s">
+      <c r="C19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" s="12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E20" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G17" s="8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="10" t="s">
+      <c r="F20" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C21" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D21" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E21" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="G18" s="12">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="F21" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E22" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="10" t="s">
+      <c r="C23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="E23" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="G20" s="12">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="C24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="F24" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="D25" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="E25" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G21" s="8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="10" t="s">
+      <c r="F25" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" s="12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="C26" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="G22" s="12">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="E26" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="12">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" s="8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="G26" s="12">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="G28" s="12">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="G30" s="12">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="E31" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="F31" s="33"/>
-      <c r="G31" s="23">
+      <c r="F26" s="33"/>
+      <c r="G26" s="23">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E26:F26"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C13" xr:uid="{E2A78460-8C3B-6A42-80E6-39597F984752}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C9" xr:uid="{E2A78460-8C3B-6A42-80E6-39597F984752}">
       <formula1>"Layer,Component,Service,Other,Technology"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1644,25 +1464,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="56" x14ac:dyDescent="0.2">
@@ -1670,16 +1490,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="F2" s="26"/>
       <c r="G2" s="26">
@@ -1691,19 +1511,19 @@
         <v>0</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="G3" s="28">
         <v>42</v>
@@ -1714,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="F4" s="26"/>
       <c r="G4" s="26">
@@ -1735,16 +1555,16 @@
         <v>0</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="F5" s="28"/>
       <c r="G5" s="28">
@@ -1756,16 +1576,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="26">
@@ -1777,16 +1597,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="F7" s="28"/>
       <c r="G7" s="28">

--- a/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FED029-EF7C-124A-B44C-3DEA7AB1033F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC59B03C-626D-484E-9BF1-12ABB62CBD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" activeTab="1" xr2:uid="{CB0C4F64-FD59-E444-AAE5-C8229608F4B9}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{CB0C4F64-FD59-E444-AAE5-C8229608F4B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="102">
   <si>
     <t>CF_M08</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Security Service</t>
   </si>
   <si>
-    <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
-  </si>
-  <si>
     <t>CF_M08_AU03</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
     <t>System Service</t>
   </si>
   <si>
-    <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
-  </si>
-  <si>
     <t>CF_M08_AU24</t>
   </si>
   <si>
@@ -122,27 +116,15 @@
     <t>Data Service</t>
   </si>
   <si>
-    <t>Data Service: • Provides the relational database to store application data. • Communicates directly with Prisma to manage database queries</t>
-  </si>
-  <si>
     <t>CF_M08_AU08</t>
   </si>
   <si>
     <t>PostgreSQL</t>
   </si>
   <si>
-    <t>Data Service (PostgreSQL)</t>
-  </si>
-  <si>
     <t>CF_M08_AU09</t>
   </si>
   <si>
-    <t>Prism</t>
-  </si>
-  <si>
-    <t>Prisma as ORM</t>
-  </si>
-  <si>
     <t>CF_M08_AU10</t>
   </si>
   <si>
@@ -155,9 +137,6 @@
     <t>Google</t>
   </si>
   <si>
-    <t>Use Google for user authentication</t>
-  </si>
-  <si>
     <t>CF_M08_AU12</t>
   </si>
   <si>
@@ -170,9 +149,6 @@
     <t>Amazon S3</t>
   </si>
   <si>
-    <t>Amazon S3 (for cloud)</t>
-  </si>
-  <si>
     <t>CF_M08_AU14</t>
   </si>
   <si>
@@ -185,9 +161,6 @@
     <t>Stripe</t>
   </si>
   <si>
-    <t>Integrate with Stripe to handle payments and subscriptions</t>
-  </si>
-  <si>
     <t>CF_M08_AU16</t>
   </si>
   <si>
@@ -212,9 +185,6 @@
     <t>Sentry</t>
   </si>
   <si>
-    <t>Use Sentry to track and manage errors in the application</t>
-  </si>
-  <si>
     <t>CF_M08_AU20</t>
   </si>
   <si>
@@ -339,6 +309,39 @@
   </si>
   <si>
     <t>CF_M08_AU04, CF_M08_AU10, CF_M08_AU12, CF_M08_AU14, CF_M08_AU16, CF_M08_AU18, CF_M08_AU20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It serves the web application using React. </t>
+  </si>
+  <si>
+    <t>Data Service: • Provides the relational database to store application data.</t>
+  </si>
+  <si>
+    <t>Prisma</t>
+  </si>
+  <si>
+    <t>It works as a reverse proxy and load balancer.</t>
+  </si>
+  <si>
+    <t>Communicates with the PostgreSQL database service (Data Service) using Prisma as ORM (Object-Relational Mapping).</t>
+  </si>
+  <si>
+    <t>Authentication: Use Google for user authentication.</t>
+  </si>
+  <si>
+    <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
+  </si>
+  <si>
+    <t>Payment processing: Integrates with Stripe to manage payments and subscriptions tions.</t>
+  </si>
+  <si>
+    <t>Analytics: Implement Google Analytics to track and analyze the traffic of the site.</t>
+  </si>
+  <si>
+    <t>Error monitoring: Use Sentry to track and manage errors in the application.</t>
+  </si>
+  <si>
+    <t>Connects to Brevo to create, send and schedule emails electronics.</t>
   </si>
 </sst>
 </file>
@@ -854,25 +857,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -892,7 +895,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G2" s="4">
         <v>41</v>
@@ -912,10 +915,10 @@
         <v>7</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G3" s="8">
         <v>41</v>
@@ -926,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>5</v>
@@ -949,19 +952,19 @@
         <v>0</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G5" s="8">
         <v>42</v>
@@ -972,17 +975,17 @@
         <v>0</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G6" s="16">
         <v>42</v>
@@ -993,19 +996,19 @@
         <v>0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="8">
         <v>42</v>
@@ -1016,19 +1019,19 @@
         <v>0</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" s="12">
         <v>42</v>
@@ -1039,17 +1042,17 @@
         <v>0</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G9" s="20">
         <v>42</v>
@@ -1060,19 +1063,19 @@
         <v>0</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G10" s="8">
         <v>42</v>
@@ -1083,19 +1086,19 @@
         <v>0</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G11" s="12">
         <v>42</v>
@@ -1106,19 +1109,19 @@
         <v>0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G12" s="8">
         <v>42</v>
@@ -1129,19 +1132,19 @@
         <v>0</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G13" s="12">
         <v>42</v>
@@ -1152,19 +1155,19 @@
         <v>0</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G14" s="8">
         <v>42</v>
@@ -1175,19 +1178,19 @@
         <v>0</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G15" s="12">
         <v>42</v>
@@ -1198,19 +1201,19 @@
         <v>0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G16" s="8">
         <v>42</v>
@@ -1221,19 +1224,19 @@
         <v>0</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G17" s="12">
         <v>42</v>
@@ -1244,19 +1247,19 @@
         <v>0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>49</v>
+        <v>40</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G18" s="8">
         <v>42</v>
@@ -1267,19 +1270,19 @@
         <v>0</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>99</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G19" s="12">
         <v>42</v>
@@ -1290,19 +1293,19 @@
         <v>0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G20" s="8">
         <v>42</v>
@@ -1313,19 +1316,19 @@
         <v>0</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G21" s="12">
         <v>42</v>
@@ -1336,19 +1339,19 @@
         <v>0</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G22" s="8">
         <v>42</v>
@@ -1359,19 +1362,19 @@
         <v>0</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G23" s="12">
         <v>42</v>
@@ -1382,19 +1385,19 @@
         <v>0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G24" s="8">
         <v>42</v>
@@ -1405,19 +1408,19 @@
         <v>0</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G25" s="12">
         <v>42</v>
@@ -1428,16 +1431,16 @@
         <v>0</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F26" s="33"/>
       <c r="G26" s="23">
@@ -1464,25 +1467,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="56" x14ac:dyDescent="0.2">
@@ -1490,16 +1493,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F2" s="26"/>
       <c r="G2" s="26">
@@ -1511,19 +1514,19 @@
         <v>0</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" s="28">
         <v>42</v>
@@ -1534,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F4" s="26"/>
       <c r="G4" s="26">
@@ -1555,37 +1558,37 @@
         <v>0</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F5" s="28"/>
       <c r="G5" s="28">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="26">
@@ -1597,16 +1600,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F7" s="28"/>
       <c r="G7" s="28">

--- a/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC59B03C-626D-484E-9BF1-12ABB62CBD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3F6A9B-71F7-814F-A14F-189743160941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{CB0C4F64-FD59-E444-AAE5-C8229608F4B9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="103">
   <si>
     <t>CF_M08</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>Connects to Brevo to create, send and schedule emails electronics.</t>
+  </si>
+  <si>
+    <t>Fixed Type</t>
   </si>
 </sst>
 </file>
@@ -852,10 +855,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D99AB4DB-819F-1A4D-945A-3D2CEBF42CB0}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>59</v>
       </c>
@@ -877,8 +880,11 @@
       <c r="G1" s="24" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="24" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -901,7 +907,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -924,7 +930,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
@@ -947,7 +953,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>0</v>
       </c>
@@ -970,7 +976,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>0</v>
       </c>
@@ -991,7 +997,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>0</v>
       </c>
@@ -1014,7 +1020,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>0</v>
       </c>
@@ -1037,7 +1043,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>0</v>
       </c>
@@ -1058,7 +1064,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>0</v>
       </c>
@@ -1081,7 +1087,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>0</v>
       </c>
@@ -1104,7 +1110,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>0</v>
       </c>
@@ -1127,7 +1133,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>0</v>
       </c>
@@ -1150,7 +1156,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>0</v>
       </c>
@@ -1173,7 +1179,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>0</v>
       </c>
@@ -1196,7 +1202,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>0</v>
       </c>
@@ -1574,7 +1580,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
         <v>0</v>
       </c>

--- a/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M08_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3F6A9B-71F7-814F-A14F-189743160941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBC6C75-0D9D-004E-B221-D2C32ED15E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{CB0C4F64-FD59-E444-AAE5-C8229608F4B9}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{CB0C4F64-FD59-E444-AAE5-C8229608F4B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="104">
   <si>
     <t>CF_M08</t>
   </si>
@@ -345,13 +345,16 @@
   </si>
   <si>
     <t>Fixed Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -367,23 +370,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color theme="0"/>
@@ -391,7 +377,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -414,6 +400,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF356854"/>
         <bgColor rgb="FF356854"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFF6F8F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -478,44 +470,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -539,8 +499,27 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -855,32 +834,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D99AB4DB-819F-1A4D-945A-3D2CEBF42CB0}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="10.83203125" style="20"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="4" t="s">
         <v>102</v>
       </c>
     </row>
@@ -903,554 +885,574 @@
       <c r="F2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="22">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="23">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="22">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="22">
         <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="10" t="s">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="22">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="18" t="s">
+      <c r="A9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="10" t="s">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="22">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="A12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="10" t="s">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="22">
         <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="F14" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="10" t="s">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="22">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="8">
+      <c r="F16" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="10" t="s">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="22">
         <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="A18" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" s="8">
+      <c r="F18" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="10" t="s">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="22">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="A20" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="8">
+      <c r="F20" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="10" t="s">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="22">
         <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="8">
+      <c r="F22" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="10" t="s">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="22">
         <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="6" t="s">
+      <c r="A24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G24" s="8">
+      <c r="F24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="10" t="s">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="22">
         <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="22" t="s">
+      <c r="A26" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="F26" s="33"/>
-      <c r="G26" s="23">
+      <c r="F26" s="21"/>
+      <c r="G26" s="24">
         <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="17"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="17"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="17"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D30" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1468,157 +1470,163 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FDF93E-8C03-3C45-9B1D-8C347BC76257}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="10.83203125" style="20"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="19" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="A2" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="26" t="s">
+      <c r="H1" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="56" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26">
+      <c r="F2" s="6"/>
+      <c r="G2" s="11">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="28" t="s">
+    <row r="3" spans="1:8" ht="306" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="28">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="182" x14ac:dyDescent="0.2">
-      <c r="A4" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="26" t="s">
+      <c r="G3" s="10">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="182" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26">
+      <c r="F4" s="6"/>
+      <c r="G4" s="11">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="409.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="28" t="s">
+    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28">
+      <c r="F5" s="8"/>
+      <c r="G5" s="10">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="409.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="26" t="s">
+    <row r="6" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26">
+      <c r="F6" s="6"/>
+      <c r="G6" s="11">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="224" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="28" t="s">
+    <row r="7" spans="1:8" ht="224" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28">
+      <c r="F7" s="8"/>
+      <c r="G7" s="10">
         <v>78</v>
       </c>
     </row>
